--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run5/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run5/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="496">
   <si>
     <t>Filename</t>
   </si>
@@ -808,682 +808,700 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9958,0.0001,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.9882,0.0000,0.0001,0.0308</t>
-  </si>
-  <si>
-    <t>0.0481,0.0006,0.0000,0.9859</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9930,0.0001,0.0020,0.0009</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.0001,0.9995</t>
+  </si>
+  <si>
+    <t>0.9968,0.0000,0.0001,0.0028</t>
+  </si>
+  <si>
+    <t>0.0122,0.0000,0.0000,0.9984</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0003,0.0002</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0003,0.0002,0.0002</t>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0005,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9827,0.0008,0.0103,0.0001</t>
+  </si>
+  <si>
+    <t>0.0122,0.0003,0.9918,0.0001</t>
+  </si>
+  <si>
+    <t>0.5242,0.0029,0.5957,0.0000</t>
+  </si>
+  <si>
+    <t>0.0040,0.0023,0.9917,0.0005</t>
+  </si>
+  <si>
+    <t>0.8657,0.0005,0.1639,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0050,0.9918,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.1646,0.0005,0.8413,0.0008</t>
+  </si>
+  <si>
+    <t>0.0734,0.0047,0.8898,0.0018</t>
+  </si>
+  <si>
+    <t>0.0009,0.0002,0.9986,0.0002</t>
+  </si>
+  <si>
+    <t>0.0091,0.0001,0.9940,0.0000</t>
+  </si>
+  <si>
+    <t>0.1827,0.0001,0.9007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0026,0.0002,0.9979,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9996,0.0003</t>
+  </si>
+  <si>
+    <t>0.9669,0.0232,0.0023,0.0002</t>
+  </si>
+  <si>
+    <t>0.4050,0.0047,0.5431,0.0019</t>
+  </si>
+  <si>
+    <t>0.0005,0.0032,0.9992,0.0012</t>
+  </si>
+  <si>
+    <t>0.0215,0.9724,0.0045,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9813,0.0073,0.0052,0.0030</t>
+  </si>
+  <si>
+    <t>0.8981,0.1483,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9937,0.2820,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.0124,0.9949,0.0002</t>
+  </si>
+  <si>
+    <t>0.0009,0.0074,0.9557,0.0461</t>
+  </si>
+  <si>
+    <t>0.0003,0.0029,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0025,0.0003,0.9970,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.1805,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9993,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0538,0.0000,0.9992</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.9977,0.0109,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0130,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0570,0.0008,0.9506,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0020,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0007,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9984,0.0004,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0015,0.9999,0.0016</t>
+  </si>
+  <si>
+    <t>0.9984,0.0005,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9975,0.0015,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9993,0.8538,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9968,0.9933,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0020,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9977,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9932,0.0010,0.0023,0.0001</t>
+  </si>
+  <si>
+    <t>0.5335,0.1485,0.0988,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0010,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9891,0.9964,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9673,0.9941,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9942,0.0465,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9985,0.9787,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.0097,0.9965</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0005,0.9998</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.9733,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9981,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9971,0.9863,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9524,0.9486,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9983,0.9914,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.5813,0.9630,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0001</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9989,0.0003,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9656,0.0029,0.0194,0.0004</t>
-  </si>
-  <si>
-    <t>0.0191,0.0008,0.9850,0.0002</t>
-  </si>
-  <si>
-    <t>0.6430,0.0011,0.4722,0.0000</t>
-  </si>
-  <si>
-    <t>0.0029,0.0005,0.9966,0.0002</t>
-  </si>
-  <si>
-    <t>0.9933,0.0002,0.0038,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9978,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.1118,0.0046,0.8078,0.0043</t>
-  </si>
-  <si>
-    <t>0.1303,0.0006,0.8798,0.0010</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0023,0.0002,0.9976,0.0001</t>
-  </si>
-  <si>
-    <t>0.9619,0.0001,0.0582,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.0001,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0011</t>
-  </si>
-  <si>
-    <t>0.6512,0.3214,0.0089,0.0002</t>
-  </si>
-  <si>
-    <t>0.9718,0.0075,0.0082,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0041,0.9998,0.0013</t>
-  </si>
-  <si>
-    <t>0.0062,0.9754,0.0185,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0007,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.4632,0.0124,0.4528,0.0025</t>
-  </si>
-  <si>
-    <t>0.2468,0.8533,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9968,0.0082,0.0001</t>
-  </si>
-  <si>
-    <t>0.0054,0.0317,0.9735,0.0009</t>
-  </si>
-  <si>
-    <t>0.0093,0.0039,0.9543,0.0097</t>
+    <t>0.9994,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0018,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.9939,0.0001,0.0032,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9990,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.6604,0.5402,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8518,0.0005,0.1076,0.0032</t>
+  </si>
+  <si>
+    <t>0.9651,0.0022,0.0184,0.0001</t>
+  </si>
+  <si>
+    <t>0.5415,0.0054,0.3280,0.0010</t>
+  </si>
+  <si>
+    <t>0.0084,0.0012,0.9871,0.0012</t>
+  </si>
+  <si>
+    <t>0.0010,0.0009,0.0017,0.9975</t>
+  </si>
+  <si>
+    <t>0.0001,0.9988,0.1281,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9993,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.9888,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9330,0.0682,0.0019,0.0000</t>
+  </si>
+  <si>
+    <t>0.1439,0.8798,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0071,0.9944,0.0026</t>
+  </si>
+  <si>
+    <t>0.0001,0.0250,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0031,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0019,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.9920,0.0004,0.0028,0.0001</t>
+  </si>
+  <si>
+    <t>0.0310,0.0117,0.9580,0.0019</t>
+  </si>
+  <si>
+    <t>0.9975,0.0000,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.9854,0.0013,0.0047,0.0003</t>
+  </si>
+  <si>
+    <t>0.0035,0.0000,0.0005,0.9984</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9967,0.5629,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0202,0.9758,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.3505,0.6391,0.0072,0.0001</t>
+  </si>
+  <si>
+    <t>0.9942,0.0002,0.0043,0.0003</t>
+  </si>
+  <si>
+    <t>0.1856,0.0001,0.0018,0.9080</t>
+  </si>
+  <si>
+    <t>0.0007,0.0117,0.9970,0.0018</t>
+  </si>
+  <si>
+    <t>0.9312,0.0001,0.0071,0.0519</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.0023,0.9922,0.0078,0.0003</t>
+  </si>
+  <si>
+    <t>0.9854,0.0046,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.9932,0.0012,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.0291,0.8803,0.0276,0.0018</t>
+  </si>
+  <si>
+    <t>0.9640,0.0064,0.0146,0.0003</t>
+  </si>
+  <si>
+    <t>0.2148,0.8242,0.0027,0.0005</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9973,0.0014,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9309,0.0705,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9370,0.0512,0.0068,0.0004</t>
+  </si>
+  <si>
+    <t>0.3986,0.6655,0.0027,0.0001</t>
+  </si>
+  <si>
+    <t>0.9370,0.0344,0.0179,0.0012</t>
+  </si>
+  <si>
+    <t>0.9941,0.0054,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9964,0.0007,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.8362,0.1540,0.0070,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9784,0.0038,0.0019,0.0036</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0174,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0181,0.0029,0.9806,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0016,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0087,0.0007,0.9911,0.0003</t>
+  </si>
+  <si>
+    <t>0.0007,0.0003,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0014,0.9968,0.0006</t>
+  </si>
+  <si>
+    <t>0.3262,0.2513,0.1076,0.0001</t>
+  </si>
+  <si>
+    <t>0.0037,0.1464,0.8986,0.0003</t>
+  </si>
+  <si>
+    <t>0.9883,0.0012,0.0039,0.0000</t>
+  </si>
+  <si>
+    <t>0.3142,0.0225,0.3156,0.0163</t>
+  </si>
+  <si>
+    <t>0.0536,0.0029,0.9420,0.0003</t>
+  </si>
+  <si>
+    <t>0.0671,0.9542,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0044,0.9937,0.0024,0.0000</t>
+  </si>
+  <si>
+    <t>0.9768,0.0414,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9400,0.1134,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.7582,0.4420,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9955,0.0006,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9786,0.0002,0.0075,0.0021</t>
+  </si>
+  <si>
+    <t>0.9453,0.0004,0.0663,0.0004</t>
+  </si>
+  <si>
+    <t>0.4571,0.0009,0.5950,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0272,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0030,0.9991,0.0001</t>
   </si>
   <si>
     <t>0.0001,0.0002,0.9998,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.0002,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0561,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9875,0.0119,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.0291,0.0004,0.9961</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.0003,0.9973,0.0199,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.0019,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.0011,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0013,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0127,0.0013,0.9872,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0007,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0022,0.9981,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9984,0.0004,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0139,0.9999,0.0005</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9973,0.9771,0.0000</t>
+    <t>0.0008,0.0090,0.9951,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9973,0.0012,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0170,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0077,0.3630,0.6737,0.0006</t>
+  </si>
+  <si>
+    <t>0.9926,0.0002,0.0039,0.0007</t>
+  </si>
+  <si>
+    <t>0.0457,0.0016,0.9701,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0004,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0002,0.9998,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9988,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9981,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.9993,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.1056,0.0089,0.9321,0.0001</t>
-  </si>
-  <si>
-    <t>0.9472,0.0026,0.0467,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9904,0.9895,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9893,0.9823,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.0031,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.8439,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.0042,0.9982</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0003,0.9998</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9983,0.0228,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9954,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9983,0.9481,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9978,0.8107,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9972,0.9881,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9893,0.1526,0.0005</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0039,0.0161,0.9929,0.0000</t>
-  </si>
-  <si>
-    <t>0.9858,0.0002,0.0083,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9990,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9993,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9104,0.1597,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4754,0.0033,0.4328,0.0016</t>
-  </si>
-  <si>
-    <t>0.6733,0.0024,0.3027,0.0001</t>
-  </si>
-  <si>
-    <t>0.2904,0.0019,0.6507,0.0051</t>
-  </si>
-  <si>
-    <t>0.7940,0.0007,0.2148,0.0009</t>
-  </si>
-  <si>
-    <t>0.0006,0.0027,0.0070,0.9928</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0357,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9716,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.7857,0.2701,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.7629,0.2679,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.9980,0.0003,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0003,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0178,0.9924,0.0014</t>
-  </si>
-  <si>
-    <t>0.0000,0.2176,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0028,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0010,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.9959,0.0001,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.0675,0.0038,0.9309,0.0011</t>
-  </si>
-  <si>
-    <t>0.9734,0.0001,0.0330,0.0000</t>
-  </si>
-  <si>
-    <t>0.9926,0.0005,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.0066,0.0002,0.0005,0.9967</t>
-  </si>
-  <si>
-    <t>0.0000,0.9956,0.2742,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0415,0.9552,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.3418,0.6675,0.0047,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0002,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0009,0.0034,0.9979,0.0007</t>
-  </si>
-  <si>
-    <t>0.9617,0.0000,0.0019,0.0511</t>
-  </si>
-  <si>
-    <t>0.9989,0.0000,0.0000,0.0020</t>
-  </si>
-  <si>
-    <t>0.0022,0.9929,0.0051,0.0003</t>
-  </si>
-  <si>
-    <t>0.9881,0.0026,0.0032,0.0003</t>
-  </si>
-  <si>
-    <t>0.9972,0.0002,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0121,0.9499,0.0141,0.0040</t>
-  </si>
-  <si>
-    <t>0.9720,0.0088,0.0068,0.0004</t>
-  </si>
-  <si>
-    <t>0.9933,0.0034,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0003,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0004,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0000,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9539,0.0448,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9142,0.0916,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.6687,0.3395,0.0054,0.0001</t>
-  </si>
-  <si>
-    <t>0.0125,0.0134,0.9787,0.0005</t>
-  </si>
-  <si>
-    <t>0.9975,0.0023,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9903,0.0038,0.0024,0.0008</t>
-  </si>
-  <si>
-    <t>0.9007,0.0611,0.0211,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0008,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.9829,0.0043,0.0046,0.0017</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0037,0.9988,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.9996,0.0003</t>
-  </si>
-  <si>
-    <t>0.0034,0.0084,0.9914,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0762,0.0007,0.9287,0.0011</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0032,0.0033,0.9923,0.0007</t>
-  </si>
-  <si>
-    <t>0.0348,0.5424,0.2467,0.0002</t>
-  </si>
-  <si>
-    <t>0.0256,0.5282,0.3048,0.0003</t>
-  </si>
-  <si>
-    <t>0.9844,0.0009,0.0097,0.0000</t>
-  </si>
-  <si>
-    <t>0.5206,0.0091,0.2669,0.0257</t>
-  </si>
-  <si>
-    <t>0.6579,0.0057,0.2625,0.0016</t>
-  </si>
-  <si>
-    <t>0.9412,0.1019,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.5201,0.5220,0.0025,0.0000</t>
-  </si>
-  <si>
-    <t>0.9134,0.1098,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9883,0.0213,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.7167,0.4755,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9953,0.0014,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9845,0.0011,0.0075,0.0002</t>
-  </si>
-  <si>
-    <t>0.8469,0.0007,0.0828,0.0129</t>
-  </si>
-  <si>
-    <t>0.9721,0.0001,0.0293,0.0005</t>
-  </si>
-  <si>
-    <t>0.9896,0.0005,0.0050,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.0003,0.9990,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0030,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0027,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0010,0.9988,0.0002</t>
-  </si>
-  <si>
-    <t>0.9982,0.0003,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9935,0.0051,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0004,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9972,0.0025,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0008,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0037,0.9994,0.0002</t>
-  </si>
-  <si>
-    <t>0.0158,0.2798,0.7065,0.0004</t>
-  </si>
-  <si>
-    <t>0.9968,0.0002,0.0012,0.0004</t>
-  </si>
-  <si>
-    <t>0.0158,0.0025,0.9861,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0009,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.1093,0.9949,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.0002,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0006,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0009,0.9983,0.0003</t>
-  </si>
-  <si>
-    <t>0.9167,0.0002,0.1243,0.0002</t>
-  </si>
-  <si>
-    <t>0.0054,0.0004,0.9967,0.0001</t>
-  </si>
-  <si>
-    <t>0.9954,0.0002,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0022,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0010,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9973,0.0020,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0024,0.9983,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0009,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0049,0.9985,0.0001</t>
-  </si>
-  <si>
-    <t>0.0060,0.0117,0.9841,0.0003</t>
-  </si>
-  <si>
-    <t>0.0069,0.0006,0.9960,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.0005,0.9982,0.0003</t>
-  </si>
-  <si>
-    <t>0.0169,0.0028,0.9715,0.0016</t>
-  </si>
-  <si>
-    <t>0.0069,0.0001,0.9881,0.0013</t>
-  </si>
-  <si>
-    <t>0.8985,0.0001,0.0013,0.1510</t>
-  </si>
-  <si>
-    <t>0.0001,0.2952,0.0000,0.9985</t>
-  </si>
-  <si>
-    <t>0.0031,0.0000,0.0002,0.9989</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.7145,0.0012,0.0003,0.4058</t>
+    <t>0.0000,0.0067,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.0005,0.9971,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0017,0.9973,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0020,0.9979,0.0002</t>
+  </si>
+  <si>
+    <t>0.9925,0.0001,0.0058,0.0001</t>
+  </si>
+  <si>
+    <t>0.0133,0.0001,0.9923,0.0001</t>
+  </si>
+  <si>
+    <t>0.3338,0.0005,0.7329,0.0012</t>
+  </si>
+  <si>
+    <t>0.9978,0.0016,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0012,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0037,0.9960,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0049,0.9994,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0096,0.9977,0.0002</t>
+  </si>
+  <si>
+    <t>0.0022,0.0004,0.9977,0.0002</t>
+  </si>
+  <si>
+    <t>0.0021,0.0006,0.9969,0.0007</t>
+  </si>
+  <si>
+    <t>0.0968,0.0004,0.9146,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9535,0.0000,0.0015,0.0507</t>
+  </si>
+  <si>
+    <t>0.0001,0.0215,0.0001,0.9993</t>
+  </si>
+  <si>
+    <t>0.0084,0.0000,0.0002,0.9979</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9362,0.0023,0.0005,0.0309</t>
   </si>
 </sst>
 </file>
@@ -1869,7 +1887,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1883,7 +1901,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1897,7 +1915,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1911,7 +1929,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1925,7 +1943,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1939,7 +1957,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1953,7 +1971,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1967,7 +1985,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1981,7 +1999,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1995,7 +2013,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2009,7 +2027,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2023,7 +2041,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2037,7 +2055,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2051,7 +2069,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2062,10 +2080,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2079,7 +2097,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2093,7 +2111,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2107,7 +2125,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2121,7 +2139,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2135,7 +2153,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2149,7 +2167,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2163,7 +2181,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2177,7 +2195,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2191,7 +2209,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2205,7 +2223,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2219,7 +2237,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2230,10 +2248,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2247,7 +2265,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2261,7 +2279,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2275,7 +2293,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2286,10 +2304,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2303,7 +2321,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2317,7 +2335,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2331,7 +2349,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2345,7 +2363,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2356,10 +2374,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2373,7 +2391,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2387,7 +2405,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2401,7 +2419,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2415,7 +2433,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2429,7 +2447,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2443,7 +2461,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2457,7 +2475,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2471,7 +2489,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2485,7 +2503,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2499,7 +2517,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2513,7 +2531,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2527,7 +2545,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2541,7 +2559,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2555,7 +2573,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2569,7 +2587,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2583,7 +2601,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2597,7 +2615,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2611,7 +2629,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2625,7 +2643,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2639,7 +2657,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2653,7 +2671,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2667,7 +2685,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2681,7 +2699,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2695,7 +2713,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2709,7 +2727,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2723,7 +2741,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2737,7 +2755,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2751,7 +2769,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2765,7 +2783,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2779,7 +2797,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2793,7 +2811,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2807,7 +2825,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2818,10 +2836,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2835,7 +2853,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2849,7 +2867,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2863,7 +2881,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2877,7 +2895,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2891,7 +2909,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2905,7 +2923,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2919,7 +2937,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2933,7 +2951,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2947,7 +2965,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2961,7 +2979,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2975,7 +2993,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2989,7 +3007,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3000,10 +3018,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3017,7 +3035,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3031,7 +3049,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3045,7 +3063,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3059,7 +3077,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3070,10 +3088,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3087,7 +3105,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>348</v>
+        <v>275</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3101,7 +3119,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3115,7 +3133,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3129,7 +3147,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3143,7 +3161,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3157,7 +3175,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3185,7 +3203,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3199,7 +3217,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3213,7 +3231,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>354</v>
+        <v>275</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3227,7 +3245,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3241,7 +3259,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>354</v>
+        <v>271</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3255,7 +3273,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3269,7 +3287,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>354</v>
+        <v>274</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3283,7 +3301,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>354</v>
+        <v>271</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3297,7 +3315,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3311,7 +3329,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>327</v>
+        <v>358</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3325,7 +3343,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3339,7 +3357,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3353,7 +3371,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3367,7 +3385,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3381,7 +3399,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>283</v>
+        <v>363</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3395,7 +3413,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3409,7 +3427,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3423,7 +3441,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3437,7 +3455,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>283</v>
+        <v>367</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3448,10 +3466,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D115" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3465,7 +3483,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3479,7 +3497,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3490,10 +3508,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3504,10 +3522,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3521,7 +3539,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3535,7 +3553,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3549,7 +3567,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3563,7 +3581,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3577,7 +3595,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3591,7 +3609,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3605,7 +3623,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3616,10 +3634,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3633,7 +3651,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3647,7 +3665,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3661,7 +3679,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3675,7 +3693,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3689,7 +3707,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>379</v>
+        <v>271</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3703,7 +3721,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3717,7 +3735,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3731,7 +3749,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3745,7 +3763,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3759,7 +3777,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3773,7 +3791,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3787,7 +3805,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3801,7 +3819,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3815,7 +3833,7 @@
         <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3829,7 +3847,7 @@
         <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3843,7 +3861,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3857,7 +3875,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3871,7 +3889,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3885,7 +3903,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>341</v>
+        <v>396</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3899,7 +3917,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3910,10 +3928,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3927,7 +3945,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3941,7 +3959,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3955,7 +3973,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>317</v>
+        <v>400</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3969,7 +3987,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3983,7 +4001,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3997,7 +4015,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4011,7 +4029,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>354</v>
+        <v>275</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4025,7 +4043,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4039,7 +4057,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4053,7 +4071,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4067,7 +4085,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4081,7 +4099,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4095,7 +4113,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4109,7 +4127,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4123,7 +4141,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4134,10 +4152,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D164" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4151,7 +4169,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4165,7 +4183,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4179,7 +4197,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4193,7 +4211,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>379</v>
+        <v>415</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4207,7 +4225,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4221,7 +4239,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4235,7 +4253,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4249,7 +4267,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4263,7 +4281,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4277,7 +4295,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4288,10 +4306,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4302,10 +4320,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4319,7 +4337,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4333,7 +4351,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4347,7 +4365,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>348</v>
+        <v>425</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4361,7 +4379,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4375,7 +4393,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4389,7 +4407,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4403,7 +4421,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4417,7 +4435,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4431,7 +4449,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4445,7 +4463,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4459,7 +4477,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4473,7 +4491,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>426</v>
+        <v>358</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4487,7 +4505,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>327</v>
+        <v>434</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4501,7 +4519,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4515,7 +4533,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4529,7 +4547,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4540,10 +4558,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D193" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4554,10 +4572,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4571,7 +4589,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4582,10 +4600,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D196" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4596,10 +4614,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4610,10 +4628,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4627,7 +4645,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4641,7 +4659,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4655,7 +4673,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4669,7 +4687,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4683,7 +4701,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4697,7 +4715,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4711,7 +4729,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4725,7 +4743,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4736,10 +4754,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4753,7 +4771,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4767,7 +4785,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4781,7 +4799,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4795,7 +4813,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4809,7 +4827,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4823,7 +4841,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4837,7 +4855,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4851,7 +4869,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4865,7 +4883,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>453</v>
+        <v>325</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4879,7 +4897,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4893,7 +4911,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4907,7 +4925,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>456</v>
+        <v>272</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4921,7 +4939,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4935,7 +4953,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4949,7 +4967,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4963,7 +4981,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4977,7 +4995,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4991,7 +5009,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5005,7 +5023,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5019,7 +5037,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5033,7 +5051,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5047,7 +5065,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>466</v>
+        <v>318</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5061,7 +5079,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5075,7 +5093,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5089,7 +5107,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5103,7 +5121,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5114,10 +5132,10 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D234" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5131,7 +5149,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5145,7 +5163,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5159,7 +5177,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>348</v>
+        <v>479</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5173,7 +5191,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5187,7 +5205,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>354</v>
+        <v>481</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5201,7 +5219,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>348</v>
+        <v>275</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5215,7 +5233,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5229,7 +5247,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>476</v>
+        <v>275</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5243,7 +5261,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5257,7 +5275,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5271,7 +5289,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5285,7 +5303,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5299,7 +5317,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5313,7 +5331,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5327,7 +5345,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5341,7 +5359,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5355,7 +5373,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5369,7 +5387,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5383,7 +5401,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5397,7 +5415,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5411,7 +5429,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5425,7 +5443,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>
